--- a/public/modelos/biblioteca-v2/PCM-MAN-008_Falhas-e-Pareto_R00.xlsx
+++ b/public/modelos/biblioteca-v2/PCM-MAN-008_Falhas-e-Pareto_R00.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Leia-me'!$A$1:$G$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Ficha de falha'!$A$1:$E$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Registro de falhas'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Registro de falhas'!$A$1:$K$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Registro de falhas'!$A$1:$M$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Pareto'!$A$1:$K$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cadastros'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Cadastros'!$A$1:$J$30</definedName>
@@ -833,7 +833,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -1020,8 +1020,11 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1041,8 +1044,11 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1156,19 +1162,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1493,6 +1487,16 @@
         <t>Fim do reparo. Data no formato dd/mm/aaaa. Exemplo: 30/10/2026.</t>
       </text>
     </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>Peça trocada.</t>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0" shapeId="0">
+      <text>
+        <t>Responsável. Escolha na lista (preencha antes a aba Cadastros).</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1667,7 +1671,7 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>885825</colOff>
+      <colOff>847725</colOff>
       <row>0</row>
       <rowOff>47625</rowOff>
     </from>
@@ -1805,9 +1809,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tb_pcm_falhas" displayName="tb_pcm_falhas" ref="A4:K29" headerRowCount="1">
-  <autoFilter ref="A4:K29"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tb_pcm_falhas" displayName="tb_pcm_falhas" ref="A4:M29" headerRowCount="1">
+  <autoFilter ref="A4:M29"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="referencia_falha"/>
     <tableColumn id="2" name="tag"/>
     <tableColumn id="3" name="equipamento"/>
@@ -1819,6 +1823,8 @@
     <tableColumn id="9" name="fim_falha"/>
     <tableColumn id="10" name="inicio_reparo"/>
     <tableColumn id="11" name="fim_reparo"/>
+    <tableColumn id="12" name="peca"/>
+    <tableColumn id="13" name="responsavel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -2554,7 +2560,7 @@
       </c>
       <c r="D21" s="28" t="inlineStr">
         <is>
-          <t>Lance todas as falhas em uma linha cada. Os horários dão o tempo parado e o tempo de reparo.</t>
+          <t>Lance todas as falhas em uma linha cada. Os horários dão o tempo parado e o tempo de reparo. Registre a peça trocada e escolha o responsável pelo reparo, nas duas últimas colunas.</t>
         </is>
       </c>
       <c r="E21" s="29" t="n"/>
@@ -3145,20 +3151,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17.4" customWidth="1" min="1" max="1"/>
+    <col width="16.5" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
+    <col width="32.9" customWidth="1" min="5" max="5"/>
+    <col width="27.1" customWidth="1" min="6" max="6"/>
+    <col width="27.1" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="21.3" customWidth="1" min="12" max="12"/>
+    <col width="19.4" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
@@ -3174,12 +3182,14 @@
       <c r="F1" s="41" t="n"/>
       <c r="G1" s="41" t="n"/>
       <c r="H1" s="41" t="n"/>
-      <c r="I1" s="42" t="n"/>
-      <c r="J1" s="43">
+      <c r="I1" s="41" t="n"/>
+      <c r="J1" s="41" t="n"/>
+      <c r="K1" s="42" t="n"/>
+      <c r="L1" s="43">
         <f>"Rev. "&amp;'Leia-me'!$D$15&amp;"   ·   "&amp;'Leia-me'!$D$16</f>
         <v/>
       </c>
-      <c r="K1" s="42" t="n"/>
+      <c r="M1" s="42" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="71" t="n"/>
@@ -3194,12 +3204,14 @@
       <c r="F2" s="46" t="n"/>
       <c r="G2" s="46" t="n"/>
       <c r="H2" s="46" t="n"/>
-      <c r="I2" s="47" t="n"/>
-      <c r="J2" s="45">
+      <c r="I2" s="46" t="n"/>
+      <c r="J2" s="46" t="n"/>
+      <c r="K2" s="47" t="n"/>
+      <c r="L2" s="45">
         <f>"Elaborado: "&amp;'Leia-me'!$D$13&amp;"   ·   Aprovado: "&amp;'Leia-me'!$D$14</f>
         <v/>
       </c>
-      <c r="K2" s="47" t="n"/>
+      <c r="M2" s="47" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="72" t="inlineStr">
@@ -3252,9 +3264,19 @@
           <t>Início do reparo</t>
         </is>
       </c>
-      <c r="K3" s="74" t="inlineStr">
+      <c r="K3" s="73" t="inlineStr">
         <is>
           <t>Fim do reparo</t>
+        </is>
+      </c>
+      <c r="L3" s="73" t="inlineStr">
+        <is>
+          <t>Peça trocada</t>
+        </is>
+      </c>
+      <c r="M3" s="74" t="inlineStr">
+        <is>
+          <t>Responsável ▼</t>
         </is>
       </c>
     </row>
@@ -3312,6 +3334,16 @@
       <c r="K4" s="75" t="inlineStr">
         <is>
           <t>fim_reparo</t>
+        </is>
+      </c>
+      <c r="L4" s="75" t="inlineStr">
+        <is>
+          <t>peca</t>
+        </is>
+      </c>
+      <c r="M4" s="75" t="inlineStr">
+        <is>
+          <t>responsavel</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3361,9 @@
       <c r="H5" s="81" t="n"/>
       <c r="I5" s="81" t="n"/>
       <c r="J5" s="81" t="n"/>
-      <c r="K5" s="82" t="n"/>
+      <c r="K5" s="81" t="n"/>
+      <c r="L5" s="82" t="n"/>
+      <c r="M5" s="83" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="76" t="n"/>
@@ -3345,7 +3379,9 @@
       <c r="H6" s="81" t="n"/>
       <c r="I6" s="81" t="n"/>
       <c r="J6" s="81" t="n"/>
-      <c r="K6" s="82" t="n"/>
+      <c r="K6" s="81" t="n"/>
+      <c r="L6" s="82" t="n"/>
+      <c r="M6" s="83" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="76" t="n"/>
@@ -3361,7 +3397,9 @@
       <c r="H7" s="81" t="n"/>
       <c r="I7" s="81" t="n"/>
       <c r="J7" s="81" t="n"/>
-      <c r="K7" s="82" t="n"/>
+      <c r="K7" s="81" t="n"/>
+      <c r="L7" s="82" t="n"/>
+      <c r="M7" s="83" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="76" t="n"/>
@@ -3377,7 +3415,9 @@
       <c r="H8" s="81" t="n"/>
       <c r="I8" s="81" t="n"/>
       <c r="J8" s="81" t="n"/>
-      <c r="K8" s="82" t="n"/>
+      <c r="K8" s="81" t="n"/>
+      <c r="L8" s="82" t="n"/>
+      <c r="M8" s="83" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="76" t="n"/>
@@ -3393,7 +3433,9 @@
       <c r="H9" s="81" t="n"/>
       <c r="I9" s="81" t="n"/>
       <c r="J9" s="81" t="n"/>
-      <c r="K9" s="82" t="n"/>
+      <c r="K9" s="81" t="n"/>
+      <c r="L9" s="82" t="n"/>
+      <c r="M9" s="83" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="76" t="n"/>
@@ -3409,7 +3451,9 @@
       <c r="H10" s="81" t="n"/>
       <c r="I10" s="81" t="n"/>
       <c r="J10" s="81" t="n"/>
-      <c r="K10" s="82" t="n"/>
+      <c r="K10" s="81" t="n"/>
+      <c r="L10" s="82" t="n"/>
+      <c r="M10" s="83" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="76" t="n"/>
@@ -3425,7 +3469,9 @@
       <c r="H11" s="81" t="n"/>
       <c r="I11" s="81" t="n"/>
       <c r="J11" s="81" t="n"/>
-      <c r="K11" s="82" t="n"/>
+      <c r="K11" s="81" t="n"/>
+      <c r="L11" s="82" t="n"/>
+      <c r="M11" s="83" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="76" t="n"/>
@@ -3441,7 +3487,9 @@
       <c r="H12" s="81" t="n"/>
       <c r="I12" s="81" t="n"/>
       <c r="J12" s="81" t="n"/>
-      <c r="K12" s="82" t="n"/>
+      <c r="K12" s="81" t="n"/>
+      <c r="L12" s="82" t="n"/>
+      <c r="M12" s="83" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="76" t="n"/>
@@ -3457,7 +3505,9 @@
       <c r="H13" s="81" t="n"/>
       <c r="I13" s="81" t="n"/>
       <c r="J13" s="81" t="n"/>
-      <c r="K13" s="82" t="n"/>
+      <c r="K13" s="81" t="n"/>
+      <c r="L13" s="82" t="n"/>
+      <c r="M13" s="83" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="76" t="n"/>
@@ -3473,7 +3523,9 @@
       <c r="H14" s="81" t="n"/>
       <c r="I14" s="81" t="n"/>
       <c r="J14" s="81" t="n"/>
-      <c r="K14" s="82" t="n"/>
+      <c r="K14" s="81" t="n"/>
+      <c r="L14" s="82" t="n"/>
+      <c r="M14" s="83" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="76" t="n"/>
@@ -3489,7 +3541,9 @@
       <c r="H15" s="81" t="n"/>
       <c r="I15" s="81" t="n"/>
       <c r="J15" s="81" t="n"/>
-      <c r="K15" s="82" t="n"/>
+      <c r="K15" s="81" t="n"/>
+      <c r="L15" s="82" t="n"/>
+      <c r="M15" s="83" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="76" t="n"/>
@@ -3505,7 +3559,9 @@
       <c r="H16" s="81" t="n"/>
       <c r="I16" s="81" t="n"/>
       <c r="J16" s="81" t="n"/>
-      <c r="K16" s="82" t="n"/>
+      <c r="K16" s="81" t="n"/>
+      <c r="L16" s="82" t="n"/>
+      <c r="M16" s="83" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="76" t="n"/>
@@ -3521,7 +3577,9 @@
       <c r="H17" s="81" t="n"/>
       <c r="I17" s="81" t="n"/>
       <c r="J17" s="81" t="n"/>
-      <c r="K17" s="82" t="n"/>
+      <c r="K17" s="81" t="n"/>
+      <c r="L17" s="82" t="n"/>
+      <c r="M17" s="83" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="76" t="n"/>
@@ -3537,7 +3595,9 @@
       <c r="H18" s="81" t="n"/>
       <c r="I18" s="81" t="n"/>
       <c r="J18" s="81" t="n"/>
-      <c r="K18" s="82" t="n"/>
+      <c r="K18" s="81" t="n"/>
+      <c r="L18" s="82" t="n"/>
+      <c r="M18" s="83" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="76" t="n"/>
@@ -3553,7 +3613,9 @@
       <c r="H19" s="81" t="n"/>
       <c r="I19" s="81" t="n"/>
       <c r="J19" s="81" t="n"/>
-      <c r="K19" s="82" t="n"/>
+      <c r="K19" s="81" t="n"/>
+      <c r="L19" s="82" t="n"/>
+      <c r="M19" s="83" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="76" t="n"/>
@@ -3569,7 +3631,9 @@
       <c r="H20" s="81" t="n"/>
       <c r="I20" s="81" t="n"/>
       <c r="J20" s="81" t="n"/>
-      <c r="K20" s="82" t="n"/>
+      <c r="K20" s="81" t="n"/>
+      <c r="L20" s="82" t="n"/>
+      <c r="M20" s="83" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="76" t="n"/>
@@ -3585,7 +3649,9 @@
       <c r="H21" s="81" t="n"/>
       <c r="I21" s="81" t="n"/>
       <c r="J21" s="81" t="n"/>
-      <c r="K21" s="82" t="n"/>
+      <c r="K21" s="81" t="n"/>
+      <c r="L21" s="82" t="n"/>
+      <c r="M21" s="83" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="76" t="n"/>
@@ -3601,7 +3667,9 @@
       <c r="H22" s="81" t="n"/>
       <c r="I22" s="81" t="n"/>
       <c r="J22" s="81" t="n"/>
-      <c r="K22" s="82" t="n"/>
+      <c r="K22" s="81" t="n"/>
+      <c r="L22" s="82" t="n"/>
+      <c r="M22" s="83" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="76" t="n"/>
@@ -3617,7 +3685,9 @@
       <c r="H23" s="81" t="n"/>
       <c r="I23" s="81" t="n"/>
       <c r="J23" s="81" t="n"/>
-      <c r="K23" s="82" t="n"/>
+      <c r="K23" s="81" t="n"/>
+      <c r="L23" s="82" t="n"/>
+      <c r="M23" s="83" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="76" t="n"/>
@@ -3633,7 +3703,9 @@
       <c r="H24" s="81" t="n"/>
       <c r="I24" s="81" t="n"/>
       <c r="J24" s="81" t="n"/>
-      <c r="K24" s="82" t="n"/>
+      <c r="K24" s="81" t="n"/>
+      <c r="L24" s="82" t="n"/>
+      <c r="M24" s="83" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="76" t="n"/>
@@ -3649,7 +3721,9 @@
       <c r="H25" s="81" t="n"/>
       <c r="I25" s="81" t="n"/>
       <c r="J25" s="81" t="n"/>
-      <c r="K25" s="82" t="n"/>
+      <c r="K25" s="81" t="n"/>
+      <c r="L25" s="82" t="n"/>
+      <c r="M25" s="83" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="76" t="n"/>
@@ -3665,7 +3739,9 @@
       <c r="H26" s="81" t="n"/>
       <c r="I26" s="81" t="n"/>
       <c r="J26" s="81" t="n"/>
-      <c r="K26" s="82" t="n"/>
+      <c r="K26" s="81" t="n"/>
+      <c r="L26" s="82" t="n"/>
+      <c r="M26" s="83" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="76" t="n"/>
@@ -3681,7 +3757,9 @@
       <c r="H27" s="81" t="n"/>
       <c r="I27" s="81" t="n"/>
       <c r="J27" s="81" t="n"/>
-      <c r="K27" s="82" t="n"/>
+      <c r="K27" s="81" t="n"/>
+      <c r="L27" s="82" t="n"/>
+      <c r="M27" s="83" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="76" t="n"/>
@@ -3697,26 +3775,30 @@
       <c r="H28" s="81" t="n"/>
       <c r="I28" s="81" t="n"/>
       <c r="J28" s="81" t="n"/>
-      <c r="K28" s="82" t="n"/>
+      <c r="K28" s="81" t="n"/>
+      <c r="L28" s="82" t="n"/>
+      <c r="M28" s="83" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="83" t="n"/>
-      <c r="B29" s="84" t="n"/>
-      <c r="C29" s="85">
+      <c r="A29" s="84" t="n"/>
+      <c r="B29" s="85" t="n"/>
+      <c r="C29" s="86">
         <f>IF(B29="","",IFERROR(INDEX(tb_pcm_ativos[descricao_ativo],MATCH(B29,tb_pcm_ativos[tag],0)),"fora do cadastro"))</f>
         <v/>
       </c>
-      <c r="D29" s="86" t="n"/>
-      <c r="E29" s="87" t="n"/>
-      <c r="F29" s="87" t="n"/>
-      <c r="G29" s="87" t="n"/>
-      <c r="H29" s="88" t="n"/>
-      <c r="I29" s="88" t="n"/>
-      <c r="J29" s="88" t="n"/>
+      <c r="D29" s="87" t="n"/>
+      <c r="E29" s="88" t="n"/>
+      <c r="F29" s="88" t="n"/>
+      <c r="G29" s="88" t="n"/>
+      <c r="H29" s="89" t="n"/>
+      <c r="I29" s="89" t="n"/>
+      <c r="J29" s="89" t="n"/>
       <c r="K29" s="89" t="n"/>
+      <c r="L29" s="90" t="n"/>
+      <c r="M29" s="91" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="90" t="inlineStr">
+      <c r="A30" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -3724,14 +3806,14 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:C2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D1:K1"/>
+    <mergeCell ref="D2:K2"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A30:M30"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="B5:B29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list" errorStyle="stop">
       <formula1>L_TAGS</formula1>
     </dataValidation>
@@ -3750,6 +3832,9 @@
     <dataValidation sqref="K5:K29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Data inválida" error="Digite uma data válida (dd/mm/aaaa)." type="date" errorStyle="stop" operator="between">
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list" errorStyle="stop">
+      <formula1>L_PESSOAS</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3798,44 +3883,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
-      <c r="A1" s="91" t="n"/>
-      <c r="B1" s="92" t="n"/>
-      <c r="C1" s="93" t="inlineStr">
+      <c r="A1" s="93" t="n"/>
+      <c r="B1" s="94" t="n"/>
+      <c r="C1" s="95" t="inlineStr">
         <is>
           <t>Pareto</t>
         </is>
       </c>
-      <c r="D1" s="94" t="n"/>
-      <c r="E1" s="94" t="n"/>
-      <c r="F1" s="94" t="n"/>
-      <c r="G1" s="94" t="n"/>
-      <c r="H1" s="92" t="n"/>
-      <c r="I1" s="95">
+      <c r="D1" s="96" t="n"/>
+      <c r="E1" s="96" t="n"/>
+      <c r="F1" s="96" t="n"/>
+      <c r="G1" s="96" t="n"/>
+      <c r="H1" s="94" t="n"/>
+      <c r="I1" s="97">
         <f>"Rev. "&amp;'Leia-me'!$D$15&amp;"   ·   "&amp;'Leia-me'!$D$16</f>
         <v/>
       </c>
-      <c r="J1" s="94" t="n"/>
-      <c r="K1" s="92" t="n"/>
+      <c r="J1" s="96" t="n"/>
+      <c r="K1" s="94" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="96" t="n"/>
-      <c r="B2" s="97" t="n"/>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="A2" s="98" t="n"/>
+      <c r="B2" s="99" t="n"/>
+      <c r="C2" s="100" t="inlineStr">
         <is>
           <t>Objetivo: Contar falhas e paradas e ver os poucos vitais que respondem por 80% do problema</t>
         </is>
       </c>
-      <c r="D2" s="99" t="n"/>
-      <c r="E2" s="99" t="n"/>
-      <c r="F2" s="99" t="n"/>
-      <c r="G2" s="99" t="n"/>
-      <c r="H2" s="97" t="n"/>
-      <c r="I2" s="98">
+      <c r="D2" s="101" t="n"/>
+      <c r="E2" s="101" t="n"/>
+      <c r="F2" s="101" t="n"/>
+      <c r="G2" s="101" t="n"/>
+      <c r="H2" s="99" t="n"/>
+      <c r="I2" s="100">
         <f>"Elaborado: "&amp;'Leia-me'!$D$13&amp;"   ·   Aprovado: "&amp;'Leia-me'!$D$14</f>
         <v/>
       </c>
-      <c r="J2" s="99" t="n"/>
-      <c r="K2" s="97" t="n"/>
+      <c r="J2" s="101" t="n"/>
+      <c r="K2" s="99" t="n"/>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="48" t="inlineStr">
@@ -3843,41 +3928,41 @@
           <t>Área ou linha</t>
         </is>
       </c>
-      <c r="B3" s="100" t="n"/>
+      <c r="B3" s="102" t="n"/>
       <c r="C3" s="49" t="inlineStr">
         <is>
           <t>O que se conta (defeito, causa, motivo de parada)</t>
         </is>
       </c>
-      <c r="D3" s="100" t="n"/>
-      <c r="E3" s="100" t="n"/>
-      <c r="F3" s="101" t="n"/>
+      <c r="D3" s="102" t="n"/>
+      <c r="E3" s="102" t="n"/>
+      <c r="F3" s="103" t="n"/>
       <c r="G3" s="49" t="inlineStr">
         <is>
           <t>Período (de ... a ...)</t>
         </is>
       </c>
-      <c r="H3" s="100" t="n"/>
+      <c r="H3" s="102" t="n"/>
       <c r="I3" s="50" t="inlineStr">
         <is>
           <t>Ordenar por</t>
         </is>
       </c>
-      <c r="J3" s="100" t="n"/>
-      <c r="K3" s="102" t="n"/>
+      <c r="J3" s="102" t="n"/>
+      <c r="K3" s="104" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="103" t="n"/>
-      <c r="B4" s="104" t="n"/>
-      <c r="C4" s="103" t="n"/>
+      <c r="A4" s="105" t="n"/>
+      <c r="B4" s="106" t="n"/>
+      <c r="C4" s="105" t="n"/>
       <c r="D4" s="20" t="n"/>
-      <c r="E4" s="104" t="n"/>
-      <c r="F4" s="105" t="n"/>
-      <c r="G4" s="103" t="n"/>
-      <c r="H4" s="104" t="n"/>
-      <c r="I4" s="106" t="n"/>
+      <c r="E4" s="106" t="n"/>
+      <c r="F4" s="107" t="n"/>
+      <c r="G4" s="105" t="n"/>
+      <c r="H4" s="106" t="n"/>
+      <c r="I4" s="108" t="n"/>
       <c r="J4" s="20" t="n"/>
-      <c r="K4" s="104" t="n"/>
+      <c r="K4" s="106" t="n"/>
     </row>
     <row r="5" ht="8" customHeight="1">
       <c r="A5" s="55" t="n"/>
@@ -3893,7 +3978,7 @@
       <c r="K5" s="55" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="107" t="inlineStr">
+      <c r="A6" s="109" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3914,12 +3999,12 @@
           </r>
         </is>
       </c>
-      <c r="B6" s="108" t="n"/>
-      <c r="C6" s="108" t="n"/>
-      <c r="D6" s="108" t="n"/>
-      <c r="E6" s="109" t="n"/>
+      <c r="B6" s="110" t="n"/>
+      <c r="C6" s="110" t="n"/>
+      <c r="D6" s="110" t="n"/>
+      <c r="E6" s="111" t="n"/>
       <c r="F6" s="55" t="n"/>
-      <c r="G6" s="107" t="inlineStr">
+      <c r="G6" s="109" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3940,92 +4025,92 @@
           </r>
         </is>
       </c>
-      <c r="H6" s="108" t="n"/>
-      <c r="I6" s="108" t="n"/>
-      <c r="J6" s="108" t="n"/>
-      <c r="K6" s="109" t="n"/>
+      <c r="H6" s="110" t="n"/>
+      <c r="I6" s="110" t="n"/>
+      <c r="J6" s="110" t="n"/>
+      <c r="K6" s="111" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="110" t="inlineStr">
+      <c r="A7" s="112" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B7" s="111" t="inlineStr">
+      <c r="B7" s="113" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="C7" s="111" t="inlineStr">
+      <c r="C7" s="113" t="inlineStr">
         <is>
           <t>Quantidade</t>
         </is>
       </c>
-      <c r="D7" s="111" t="inlineStr">
+      <c r="D7" s="113" t="inlineStr">
         <is>
           <t>Custo por ocorrência</t>
         </is>
       </c>
-      <c r="E7" s="112" t="inlineStr">
+      <c r="E7" s="114" t="inlineStr">
         <is>
           <t>Custo total</t>
         </is>
       </c>
       <c r="F7" s="55" t="n"/>
-      <c r="G7" s="110" t="inlineStr">
+      <c r="G7" s="112" t="inlineStr">
         <is>
           <t>Pos.</t>
         </is>
       </c>
-      <c r="H7" s="111" t="inlineStr">
+      <c r="H7" s="113" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="I7" s="111" t="inlineStr">
+      <c r="I7" s="113" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J7" s="111" t="inlineStr">
+      <c r="J7" s="113" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="K7" s="112" t="inlineStr">
+      <c r="K7" s="114" t="inlineStr">
         <is>
           <t>% acumulado</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="113" t="n">
+      <c r="A8" s="115" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="114" t="n"/>
-      <c r="C8" s="115" t="n"/>
-      <c r="D8" s="116" t="n"/>
-      <c r="E8" s="117">
+      <c r="B8" s="116" t="n"/>
+      <c r="C8" s="117" t="n"/>
+      <c r="D8" s="118" t="n"/>
+      <c r="E8" s="119">
         <f>IF(AND(ISNUMBER(C8),ISNUMBER(D8)),C8*D8,"")</f>
         <v/>
       </c>
       <c r="F8" s="55" t="n"/>
-      <c r="G8" s="113" t="n">
+      <c r="G8" s="115" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="114">
+      <c r="H8" s="116">
         <f>IF(M8="","",INDEX($B$8:$B$17,M8))</f>
         <v/>
       </c>
-      <c r="I8" s="118">
+      <c r="I8" s="120">
         <f>IF(M8="","",IF($I$4="Custo total",INDEX($E$8:$E$17,M8),INDEX($C$8:$C$17,M8)))</f>
         <v/>
       </c>
-      <c r="J8" s="119">
+      <c r="J8" s="121">
         <f>IF(OR(I8="",$I$18=0),"",I8/$I$18)</f>
         <v/>
       </c>
-      <c r="K8" s="120">
+      <c r="K8" s="122">
         <f>IF(J8="","",SUM($J$8:J8))</f>
         <v/>
       </c>
@@ -4043,33 +4128,33 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="113" t="n">
+      <c r="A9" s="115" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="114" t="n"/>
-      <c r="C9" s="115" t="n"/>
-      <c r="D9" s="116" t="n"/>
-      <c r="E9" s="117">
+      <c r="B9" s="116" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="118" t="n"/>
+      <c r="E9" s="119">
         <f>IF(AND(ISNUMBER(C9),ISNUMBER(D9)),C9*D9,"")</f>
         <v/>
       </c>
       <c r="F9" s="55" t="n"/>
-      <c r="G9" s="113" t="n">
+      <c r="G9" s="115" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="114">
+      <c r="H9" s="116">
         <f>IF(M9="","",INDEX($B$8:$B$17,M9))</f>
         <v/>
       </c>
-      <c r="I9" s="118">
+      <c r="I9" s="120">
         <f>IF(M9="","",IF($I$4="Custo total",INDEX($E$8:$E$17,M9),INDEX($C$8:$C$17,M9)))</f>
         <v/>
       </c>
-      <c r="J9" s="119">
+      <c r="J9" s="121">
         <f>IF(OR(I9="",$I$18=0),"",I9/$I$18)</f>
         <v/>
       </c>
-      <c r="K9" s="120">
+      <c r="K9" s="122">
         <f>IF(J9="","",SUM($J$8:J9))</f>
         <v/>
       </c>
@@ -4087,33 +4172,33 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="113" t="n">
+      <c r="A10" s="115" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="114" t="n"/>
-      <c r="C10" s="115" t="n"/>
-      <c r="D10" s="116" t="n"/>
-      <c r="E10" s="117">
+      <c r="B10" s="116" t="n"/>
+      <c r="C10" s="117" t="n"/>
+      <c r="D10" s="118" t="n"/>
+      <c r="E10" s="119">
         <f>IF(AND(ISNUMBER(C10),ISNUMBER(D10)),C10*D10,"")</f>
         <v/>
       </c>
       <c r="F10" s="55" t="n"/>
-      <c r="G10" s="113" t="n">
+      <c r="G10" s="115" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="114">
+      <c r="H10" s="116">
         <f>IF(M10="","",INDEX($B$8:$B$17,M10))</f>
         <v/>
       </c>
-      <c r="I10" s="118">
+      <c r="I10" s="120">
         <f>IF(M10="","",IF($I$4="Custo total",INDEX($E$8:$E$17,M10),INDEX($C$8:$C$17,M10)))</f>
         <v/>
       </c>
-      <c r="J10" s="119">
+      <c r="J10" s="121">
         <f>IF(OR(I10="",$I$18=0),"",I10/$I$18)</f>
         <v/>
       </c>
-      <c r="K10" s="120">
+      <c r="K10" s="122">
         <f>IF(J10="","",SUM($J$8:J10))</f>
         <v/>
       </c>
@@ -4131,33 +4216,33 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="113" t="n">
+      <c r="A11" s="115" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="114" t="n"/>
-      <c r="C11" s="115" t="n"/>
-      <c r="D11" s="116" t="n"/>
-      <c r="E11" s="117">
+      <c r="B11" s="116" t="n"/>
+      <c r="C11" s="117" t="n"/>
+      <c r="D11" s="118" t="n"/>
+      <c r="E11" s="119">
         <f>IF(AND(ISNUMBER(C11),ISNUMBER(D11)),C11*D11,"")</f>
         <v/>
       </c>
       <c r="F11" s="55" t="n"/>
-      <c r="G11" s="113" t="n">
+      <c r="G11" s="115" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="114">
+      <c r="H11" s="116">
         <f>IF(M11="","",INDEX($B$8:$B$17,M11))</f>
         <v/>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="120">
         <f>IF(M11="","",IF($I$4="Custo total",INDEX($E$8:$E$17,M11),INDEX($C$8:$C$17,M11)))</f>
         <v/>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="121">
         <f>IF(OR(I11="",$I$18=0),"",I11/$I$18)</f>
         <v/>
       </c>
-      <c r="K11" s="120">
+      <c r="K11" s="122">
         <f>IF(J11="","",SUM($J$8:J11))</f>
         <v/>
       </c>
@@ -4175,33 +4260,33 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="113" t="n">
+      <c r="A12" s="115" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="114" t="n"/>
-      <c r="C12" s="115" t="n"/>
-      <c r="D12" s="116" t="n"/>
-      <c r="E12" s="117">
+      <c r="B12" s="116" t="n"/>
+      <c r="C12" s="117" t="n"/>
+      <c r="D12" s="118" t="n"/>
+      <c r="E12" s="119">
         <f>IF(AND(ISNUMBER(C12),ISNUMBER(D12)),C12*D12,"")</f>
         <v/>
       </c>
       <c r="F12" s="55" t="n"/>
-      <c r="G12" s="113" t="n">
+      <c r="G12" s="115" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="114">
+      <c r="H12" s="116">
         <f>IF(M12="","",INDEX($B$8:$B$17,M12))</f>
         <v/>
       </c>
-      <c r="I12" s="118">
+      <c r="I12" s="120">
         <f>IF(M12="","",IF($I$4="Custo total",INDEX($E$8:$E$17,M12),INDEX($C$8:$C$17,M12)))</f>
         <v/>
       </c>
-      <c r="J12" s="119">
+      <c r="J12" s="121">
         <f>IF(OR(I12="",$I$18=0),"",I12/$I$18)</f>
         <v/>
       </c>
-      <c r="K12" s="120">
+      <c r="K12" s="122">
         <f>IF(J12="","",SUM($J$8:J12))</f>
         <v/>
       </c>
@@ -4219,33 +4304,33 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="113" t="n">
+      <c r="A13" s="115" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="114" t="n"/>
-      <c r="C13" s="115" t="n"/>
-      <c r="D13" s="116" t="n"/>
-      <c r="E13" s="117">
+      <c r="B13" s="116" t="n"/>
+      <c r="C13" s="117" t="n"/>
+      <c r="D13" s="118" t="n"/>
+      <c r="E13" s="119">
         <f>IF(AND(ISNUMBER(C13),ISNUMBER(D13)),C13*D13,"")</f>
         <v/>
       </c>
       <c r="F13" s="55" t="n"/>
-      <c r="G13" s="113" t="n">
+      <c r="G13" s="115" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="114">
+      <c r="H13" s="116">
         <f>IF(M13="","",INDEX($B$8:$B$17,M13))</f>
         <v/>
       </c>
-      <c r="I13" s="118">
+      <c r="I13" s="120">
         <f>IF(M13="","",IF($I$4="Custo total",INDEX($E$8:$E$17,M13),INDEX($C$8:$C$17,M13)))</f>
         <v/>
       </c>
-      <c r="J13" s="119">
+      <c r="J13" s="121">
         <f>IF(OR(I13="",$I$18=0),"",I13/$I$18)</f>
         <v/>
       </c>
-      <c r="K13" s="120">
+      <c r="K13" s="122">
         <f>IF(J13="","",SUM($J$8:J13))</f>
         <v/>
       </c>
@@ -4263,33 +4348,33 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="113" t="n">
+      <c r="A14" s="115" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="114" t="n"/>
-      <c r="C14" s="115" t="n"/>
-      <c r="D14" s="116" t="n"/>
-      <c r="E14" s="117">
+      <c r="B14" s="116" t="n"/>
+      <c r="C14" s="117" t="n"/>
+      <c r="D14" s="118" t="n"/>
+      <c r="E14" s="119">
         <f>IF(AND(ISNUMBER(C14),ISNUMBER(D14)),C14*D14,"")</f>
         <v/>
       </c>
       <c r="F14" s="55" t="n"/>
-      <c r="G14" s="113" t="n">
+      <c r="G14" s="115" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="114">
+      <c r="H14" s="116">
         <f>IF(M14="","",INDEX($B$8:$B$17,M14))</f>
         <v/>
       </c>
-      <c r="I14" s="118">
+      <c r="I14" s="120">
         <f>IF(M14="","",IF($I$4="Custo total",INDEX($E$8:$E$17,M14),INDEX($C$8:$C$17,M14)))</f>
         <v/>
       </c>
-      <c r="J14" s="119">
+      <c r="J14" s="121">
         <f>IF(OR(I14="",$I$18=0),"",I14/$I$18)</f>
         <v/>
       </c>
-      <c r="K14" s="120">
+      <c r="K14" s="122">
         <f>IF(J14="","",SUM($J$8:J14))</f>
         <v/>
       </c>
@@ -4307,33 +4392,33 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="113" t="n">
+      <c r="A15" s="115" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="114" t="n"/>
-      <c r="C15" s="115" t="n"/>
-      <c r="D15" s="116" t="n"/>
-      <c r="E15" s="117">
+      <c r="B15" s="116" t="n"/>
+      <c r="C15" s="117" t="n"/>
+      <c r="D15" s="118" t="n"/>
+      <c r="E15" s="119">
         <f>IF(AND(ISNUMBER(C15),ISNUMBER(D15)),C15*D15,"")</f>
         <v/>
       </c>
       <c r="F15" s="55" t="n"/>
-      <c r="G15" s="113" t="n">
+      <c r="G15" s="115" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="114">
+      <c r="H15" s="116">
         <f>IF(M15="","",INDEX($B$8:$B$17,M15))</f>
         <v/>
       </c>
-      <c r="I15" s="118">
+      <c r="I15" s="120">
         <f>IF(M15="","",IF($I$4="Custo total",INDEX($E$8:$E$17,M15),INDEX($C$8:$C$17,M15)))</f>
         <v/>
       </c>
-      <c r="J15" s="119">
+      <c r="J15" s="121">
         <f>IF(OR(I15="",$I$18=0),"",I15/$I$18)</f>
         <v/>
       </c>
-      <c r="K15" s="120">
+      <c r="K15" s="122">
         <f>IF(J15="","",SUM($J$8:J15))</f>
         <v/>
       </c>
@@ -4351,33 +4436,33 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="113" t="n">
+      <c r="A16" s="115" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="114" t="n"/>
-      <c r="C16" s="115" t="n"/>
-      <c r="D16" s="116" t="n"/>
-      <c r="E16" s="117">
+      <c r="B16" s="116" t="n"/>
+      <c r="C16" s="117" t="n"/>
+      <c r="D16" s="118" t="n"/>
+      <c r="E16" s="119">
         <f>IF(AND(ISNUMBER(C16),ISNUMBER(D16)),C16*D16,"")</f>
         <v/>
       </c>
       <c r="F16" s="55" t="n"/>
-      <c r="G16" s="113" t="n">
+      <c r="G16" s="115" t="n">
         <v>9</v>
       </c>
-      <c r="H16" s="114">
+      <c r="H16" s="116">
         <f>IF(M16="","",INDEX($B$8:$B$17,M16))</f>
         <v/>
       </c>
-      <c r="I16" s="118">
+      <c r="I16" s="120">
         <f>IF(M16="","",IF($I$4="Custo total",INDEX($E$8:$E$17,M16),INDEX($C$8:$C$17,M16)))</f>
         <v/>
       </c>
-      <c r="J16" s="119">
+      <c r="J16" s="121">
         <f>IF(OR(I16="",$I$18=0),"",I16/$I$18)</f>
         <v/>
       </c>
-      <c r="K16" s="120">
+      <c r="K16" s="122">
         <f>IF(J16="","",SUM($J$8:J16))</f>
         <v/>
       </c>
@@ -4395,33 +4480,33 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="121" t="n">
+      <c r="A17" s="123" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="122" t="n"/>
-      <c r="C17" s="123" t="n"/>
-      <c r="D17" s="124" t="n"/>
-      <c r="E17" s="125">
+      <c r="B17" s="124" t="n"/>
+      <c r="C17" s="125" t="n"/>
+      <c r="D17" s="126" t="n"/>
+      <c r="E17" s="127">
         <f>IF(AND(ISNUMBER(C17),ISNUMBER(D17)),C17*D17,"")</f>
         <v/>
       </c>
       <c r="F17" s="55" t="n"/>
-      <c r="G17" s="121" t="n">
+      <c r="G17" s="123" t="n">
         <v>10</v>
       </c>
-      <c r="H17" s="122">
+      <c r="H17" s="124">
         <f>IF(M17="","",INDEX($B$8:$B$17,M17))</f>
         <v/>
       </c>
-      <c r="I17" s="126">
+      <c r="I17" s="128">
         <f>IF(M17="","",IF($I$4="Custo total",INDEX($E$8:$E$17,M17),INDEX($C$8:$C$17,M17)))</f>
         <v/>
       </c>
-      <c r="J17" s="127">
+      <c r="J17" s="129">
         <f>IF(OR(I17="",$I$18=0),"",I17/$I$18)</f>
         <v/>
       </c>
-      <c r="K17" s="128">
+      <c r="K17" s="130">
         <f>IF(J17="","",SUM($J$8:J17))</f>
         <v/>
       </c>
@@ -4439,34 +4524,34 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="129" t="n"/>
-      <c r="B18" s="130" t="inlineStr">
+      <c r="A18" s="131" t="n"/>
+      <c r="B18" s="132" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="131">
+      <c r="C18" s="133">
         <f>SUM(C8:C17)</f>
         <v/>
       </c>
       <c r="D18" s="20" t="n"/>
-      <c r="E18" s="132">
+      <c r="E18" s="134">
         <f>SUM(E8:E17)</f>
         <v/>
       </c>
       <c r="F18" s="55" t="n"/>
-      <c r="G18" s="129" t="n"/>
-      <c r="H18" s="130" t="inlineStr">
+      <c r="G18" s="131" t="n"/>
+      <c r="H18" s="132" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I18" s="133">
+      <c r="I18" s="135">
         <f>SUM(I8:I17)</f>
         <v/>
       </c>
       <c r="J18" s="20" t="n"/>
-      <c r="K18" s="104" t="n"/>
+      <c r="K18" s="106" t="n"/>
     </row>
     <row r="19" ht="8" customHeight="1">
       <c r="A19" s="55" t="n"/>
@@ -4482,7 +4567,7 @@
       <c r="K19" s="55" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="107" t="inlineStr">
+      <c r="A20" s="109" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4503,211 +4588,211 @@
           </r>
         </is>
       </c>
-      <c r="B20" s="108" t="n"/>
-      <c r="C20" s="108" t="n"/>
-      <c r="D20" s="108" t="n"/>
-      <c r="E20" s="108" t="n"/>
-      <c r="F20" s="108" t="n"/>
-      <c r="G20" s="108" t="n"/>
-      <c r="H20" s="108" t="n"/>
-      <c r="I20" s="108" t="n"/>
-      <c r="J20" s="108" t="n"/>
-      <c r="K20" s="109" t="n"/>
+      <c r="B20" s="110" t="n"/>
+      <c r="C20" s="110" t="n"/>
+      <c r="D20" s="110" t="n"/>
+      <c r="E20" s="110" t="n"/>
+      <c r="F20" s="110" t="n"/>
+      <c r="G20" s="110" t="n"/>
+      <c r="H20" s="110" t="n"/>
+      <c r="I20" s="110" t="n"/>
+      <c r="J20" s="110" t="n"/>
+      <c r="K20" s="111" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="134" t="n"/>
-      <c r="B21" s="135" t="n"/>
-      <c r="C21" s="135" t="n"/>
-      <c r="D21" s="135" t="n"/>
-      <c r="E21" s="135" t="n"/>
-      <c r="F21" s="135" t="n"/>
-      <c r="G21" s="135" t="n"/>
-      <c r="H21" s="135" t="n"/>
-      <c r="I21" s="135" t="n"/>
-      <c r="J21" s="135" t="n"/>
-      <c r="K21" s="136" t="n"/>
+      <c r="A21" s="136" t="n"/>
+      <c r="B21" s="137" t="n"/>
+      <c r="C21" s="137" t="n"/>
+      <c r="D21" s="137" t="n"/>
+      <c r="E21" s="137" t="n"/>
+      <c r="F21" s="137" t="n"/>
+      <c r="G21" s="137" t="n"/>
+      <c r="H21" s="137" t="n"/>
+      <c r="I21" s="137" t="n"/>
+      <c r="J21" s="137" t="n"/>
+      <c r="K21" s="138" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="134" t="n"/>
-      <c r="B22" s="135" t="n"/>
-      <c r="C22" s="135" t="n"/>
-      <c r="D22" s="135" t="n"/>
-      <c r="E22" s="135" t="n"/>
-      <c r="F22" s="135" t="n"/>
-      <c r="G22" s="135" t="n"/>
-      <c r="H22" s="135" t="n"/>
-      <c r="I22" s="135" t="n"/>
-      <c r="J22" s="135" t="n"/>
-      <c r="K22" s="136" t="n"/>
+      <c r="A22" s="136" t="n"/>
+      <c r="B22" s="137" t="n"/>
+      <c r="C22" s="137" t="n"/>
+      <c r="D22" s="137" t="n"/>
+      <c r="E22" s="137" t="n"/>
+      <c r="F22" s="137" t="n"/>
+      <c r="G22" s="137" t="n"/>
+      <c r="H22" s="137" t="n"/>
+      <c r="I22" s="137" t="n"/>
+      <c r="J22" s="137" t="n"/>
+      <c r="K22" s="138" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="134" t="n"/>
-      <c r="B23" s="135" t="n"/>
-      <c r="C23" s="135" t="n"/>
-      <c r="D23" s="135" t="n"/>
-      <c r="E23" s="135" t="n"/>
-      <c r="F23" s="135" t="n"/>
-      <c r="G23" s="135" t="n"/>
-      <c r="H23" s="135" t="n"/>
-      <c r="I23" s="135" t="n"/>
-      <c r="J23" s="135" t="n"/>
-      <c r="K23" s="136" t="n"/>
+      <c r="A23" s="136" t="n"/>
+      <c r="B23" s="137" t="n"/>
+      <c r="C23" s="137" t="n"/>
+      <c r="D23" s="137" t="n"/>
+      <c r="E23" s="137" t="n"/>
+      <c r="F23" s="137" t="n"/>
+      <c r="G23" s="137" t="n"/>
+      <c r="H23" s="137" t="n"/>
+      <c r="I23" s="137" t="n"/>
+      <c r="J23" s="137" t="n"/>
+      <c r="K23" s="138" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="134" t="n"/>
-      <c r="B24" s="135" t="n"/>
-      <c r="C24" s="135" t="n"/>
-      <c r="D24" s="135" t="n"/>
-      <c r="E24" s="135" t="n"/>
-      <c r="F24" s="135" t="n"/>
-      <c r="G24" s="135" t="n"/>
-      <c r="H24" s="135" t="n"/>
-      <c r="I24" s="135" t="n"/>
-      <c r="J24" s="135" t="n"/>
-      <c r="K24" s="136" t="n"/>
+      <c r="A24" s="136" t="n"/>
+      <c r="B24" s="137" t="n"/>
+      <c r="C24" s="137" t="n"/>
+      <c r="D24" s="137" t="n"/>
+      <c r="E24" s="137" t="n"/>
+      <c r="F24" s="137" t="n"/>
+      <c r="G24" s="137" t="n"/>
+      <c r="H24" s="137" t="n"/>
+      <c r="I24" s="137" t="n"/>
+      <c r="J24" s="137" t="n"/>
+      <c r="K24" s="138" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="134" t="n"/>
-      <c r="B25" s="135" t="n"/>
-      <c r="C25" s="135" t="n"/>
-      <c r="D25" s="135" t="n"/>
-      <c r="E25" s="135" t="n"/>
-      <c r="F25" s="135" t="n"/>
-      <c r="G25" s="135" t="n"/>
-      <c r="H25" s="135" t="n"/>
-      <c r="I25" s="135" t="n"/>
-      <c r="J25" s="135" t="n"/>
-      <c r="K25" s="136" t="n"/>
+      <c r="A25" s="136" t="n"/>
+      <c r="B25" s="137" t="n"/>
+      <c r="C25" s="137" t="n"/>
+      <c r="D25" s="137" t="n"/>
+      <c r="E25" s="137" t="n"/>
+      <c r="F25" s="137" t="n"/>
+      <c r="G25" s="137" t="n"/>
+      <c r="H25" s="137" t="n"/>
+      <c r="I25" s="137" t="n"/>
+      <c r="J25" s="137" t="n"/>
+      <c r="K25" s="138" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="134" t="n"/>
-      <c r="B26" s="135" t="n"/>
-      <c r="C26" s="135" t="n"/>
-      <c r="D26" s="135" t="n"/>
-      <c r="E26" s="135" t="n"/>
-      <c r="F26" s="135" t="n"/>
-      <c r="G26" s="135" t="n"/>
-      <c r="H26" s="135" t="n"/>
-      <c r="I26" s="135" t="n"/>
-      <c r="J26" s="135" t="n"/>
-      <c r="K26" s="136" t="n"/>
+      <c r="A26" s="136" t="n"/>
+      <c r="B26" s="137" t="n"/>
+      <c r="C26" s="137" t="n"/>
+      <c r="D26" s="137" t="n"/>
+      <c r="E26" s="137" t="n"/>
+      <c r="F26" s="137" t="n"/>
+      <c r="G26" s="137" t="n"/>
+      <c r="H26" s="137" t="n"/>
+      <c r="I26" s="137" t="n"/>
+      <c r="J26" s="137" t="n"/>
+      <c r="K26" s="138" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="134" t="n"/>
-      <c r="B27" s="135" t="n"/>
-      <c r="C27" s="135" t="n"/>
-      <c r="D27" s="135" t="n"/>
-      <c r="E27" s="135" t="n"/>
-      <c r="F27" s="135" t="n"/>
-      <c r="G27" s="135" t="n"/>
-      <c r="H27" s="135" t="n"/>
-      <c r="I27" s="135" t="n"/>
-      <c r="J27" s="135" t="n"/>
-      <c r="K27" s="136" t="n"/>
+      <c r="A27" s="136" t="n"/>
+      <c r="B27" s="137" t="n"/>
+      <c r="C27" s="137" t="n"/>
+      <c r="D27" s="137" t="n"/>
+      <c r="E27" s="137" t="n"/>
+      <c r="F27" s="137" t="n"/>
+      <c r="G27" s="137" t="n"/>
+      <c r="H27" s="137" t="n"/>
+      <c r="I27" s="137" t="n"/>
+      <c r="J27" s="137" t="n"/>
+      <c r="K27" s="138" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="134" t="n"/>
-      <c r="B28" s="135" t="n"/>
-      <c r="C28" s="135" t="n"/>
-      <c r="D28" s="135" t="n"/>
-      <c r="E28" s="135" t="n"/>
-      <c r="F28" s="135" t="n"/>
-      <c r="G28" s="135" t="n"/>
-      <c r="H28" s="135" t="n"/>
-      <c r="I28" s="135" t="n"/>
-      <c r="J28" s="135" t="n"/>
-      <c r="K28" s="136" t="n"/>
+      <c r="A28" s="136" t="n"/>
+      <c r="B28" s="137" t="n"/>
+      <c r="C28" s="137" t="n"/>
+      <c r="D28" s="137" t="n"/>
+      <c r="E28" s="137" t="n"/>
+      <c r="F28" s="137" t="n"/>
+      <c r="G28" s="137" t="n"/>
+      <c r="H28" s="137" t="n"/>
+      <c r="I28" s="137" t="n"/>
+      <c r="J28" s="137" t="n"/>
+      <c r="K28" s="138" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="134" t="n"/>
-      <c r="B29" s="135" t="n"/>
-      <c r="C29" s="135" t="n"/>
-      <c r="D29" s="135" t="n"/>
-      <c r="E29" s="135" t="n"/>
-      <c r="F29" s="135" t="n"/>
-      <c r="G29" s="135" t="n"/>
-      <c r="H29" s="135" t="n"/>
-      <c r="I29" s="135" t="n"/>
-      <c r="J29" s="135" t="n"/>
-      <c r="K29" s="136" t="n"/>
+      <c r="A29" s="136" t="n"/>
+      <c r="B29" s="137" t="n"/>
+      <c r="C29" s="137" t="n"/>
+      <c r="D29" s="137" t="n"/>
+      <c r="E29" s="137" t="n"/>
+      <c r="F29" s="137" t="n"/>
+      <c r="G29" s="137" t="n"/>
+      <c r="H29" s="137" t="n"/>
+      <c r="I29" s="137" t="n"/>
+      <c r="J29" s="137" t="n"/>
+      <c r="K29" s="138" t="n"/>
     </row>
     <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="134" t="n"/>
-      <c r="B30" s="135" t="n"/>
-      <c r="C30" s="135" t="n"/>
-      <c r="D30" s="135" t="n"/>
-      <c r="E30" s="135" t="n"/>
-      <c r="F30" s="135" t="n"/>
-      <c r="G30" s="135" t="n"/>
-      <c r="H30" s="135" t="n"/>
-      <c r="I30" s="135" t="n"/>
-      <c r="J30" s="135" t="n"/>
-      <c r="K30" s="136" t="n"/>
+      <c r="A30" s="136" t="n"/>
+      <c r="B30" s="137" t="n"/>
+      <c r="C30" s="137" t="n"/>
+      <c r="D30" s="137" t="n"/>
+      <c r="E30" s="137" t="n"/>
+      <c r="F30" s="137" t="n"/>
+      <c r="G30" s="137" t="n"/>
+      <c r="H30" s="137" t="n"/>
+      <c r="I30" s="137" t="n"/>
+      <c r="J30" s="137" t="n"/>
+      <c r="K30" s="138" t="n"/>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="134" t="n"/>
-      <c r="B31" s="135" t="n"/>
-      <c r="C31" s="135" t="n"/>
-      <c r="D31" s="135" t="n"/>
-      <c r="E31" s="135" t="n"/>
-      <c r="F31" s="135" t="n"/>
-      <c r="G31" s="135" t="n"/>
-      <c r="H31" s="135" t="n"/>
-      <c r="I31" s="135" t="n"/>
-      <c r="J31" s="135" t="n"/>
-      <c r="K31" s="136" t="n"/>
+      <c r="A31" s="136" t="n"/>
+      <c r="B31" s="137" t="n"/>
+      <c r="C31" s="137" t="n"/>
+      <c r="D31" s="137" t="n"/>
+      <c r="E31" s="137" t="n"/>
+      <c r="F31" s="137" t="n"/>
+      <c r="G31" s="137" t="n"/>
+      <c r="H31" s="137" t="n"/>
+      <c r="I31" s="137" t="n"/>
+      <c r="J31" s="137" t="n"/>
+      <c r="K31" s="138" t="n"/>
     </row>
     <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="134" t="n"/>
-      <c r="B32" s="135" t="n"/>
-      <c r="C32" s="135" t="n"/>
-      <c r="D32" s="135" t="n"/>
-      <c r="E32" s="135" t="n"/>
-      <c r="F32" s="135" t="n"/>
-      <c r="G32" s="135" t="n"/>
-      <c r="H32" s="135" t="n"/>
-      <c r="I32" s="135" t="n"/>
-      <c r="J32" s="135" t="n"/>
-      <c r="K32" s="136" t="n"/>
+      <c r="A32" s="136" t="n"/>
+      <c r="B32" s="137" t="n"/>
+      <c r="C32" s="137" t="n"/>
+      <c r="D32" s="137" t="n"/>
+      <c r="E32" s="137" t="n"/>
+      <c r="F32" s="137" t="n"/>
+      <c r="G32" s="137" t="n"/>
+      <c r="H32" s="137" t="n"/>
+      <c r="I32" s="137" t="n"/>
+      <c r="J32" s="137" t="n"/>
+      <c r="K32" s="138" t="n"/>
     </row>
     <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="134" t="n"/>
-      <c r="B33" s="135" t="n"/>
-      <c r="C33" s="135" t="n"/>
-      <c r="D33" s="135" t="n"/>
-      <c r="E33" s="135" t="n"/>
-      <c r="F33" s="135" t="n"/>
-      <c r="G33" s="135" t="n"/>
-      <c r="H33" s="135" t="n"/>
-      <c r="I33" s="135" t="n"/>
-      <c r="J33" s="135" t="n"/>
-      <c r="K33" s="136" t="n"/>
+      <c r="A33" s="136" t="n"/>
+      <c r="B33" s="137" t="n"/>
+      <c r="C33" s="137" t="n"/>
+      <c r="D33" s="137" t="n"/>
+      <c r="E33" s="137" t="n"/>
+      <c r="F33" s="137" t="n"/>
+      <c r="G33" s="137" t="n"/>
+      <c r="H33" s="137" t="n"/>
+      <c r="I33" s="137" t="n"/>
+      <c r="J33" s="137" t="n"/>
+      <c r="K33" s="138" t="n"/>
     </row>
     <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="134" t="n"/>
-      <c r="B34" s="135" t="n"/>
-      <c r="C34" s="135" t="n"/>
-      <c r="D34" s="135" t="n"/>
-      <c r="E34" s="135" t="n"/>
-      <c r="F34" s="135" t="n"/>
-      <c r="G34" s="135" t="n"/>
-      <c r="H34" s="135" t="n"/>
-      <c r="I34" s="135" t="n"/>
-      <c r="J34" s="135" t="n"/>
-      <c r="K34" s="136" t="n"/>
+      <c r="A34" s="136" t="n"/>
+      <c r="B34" s="137" t="n"/>
+      <c r="C34" s="137" t="n"/>
+      <c r="D34" s="137" t="n"/>
+      <c r="E34" s="137" t="n"/>
+      <c r="F34" s="137" t="n"/>
+      <c r="G34" s="137" t="n"/>
+      <c r="H34" s="137" t="n"/>
+      <c r="I34" s="137" t="n"/>
+      <c r="J34" s="137" t="n"/>
+      <c r="K34" s="138" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="137" t="n"/>
-      <c r="B35" s="105" t="n"/>
-      <c r="C35" s="105" t="n"/>
-      <c r="D35" s="105" t="n"/>
-      <c r="E35" s="105" t="n"/>
-      <c r="F35" s="105" t="n"/>
-      <c r="G35" s="105" t="n"/>
-      <c r="H35" s="105" t="n"/>
-      <c r="I35" s="105" t="n"/>
-      <c r="J35" s="105" t="n"/>
-      <c r="K35" s="138" t="n"/>
+      <c r="A35" s="139" t="n"/>
+      <c r="B35" s="107" t="n"/>
+      <c r="C35" s="107" t="n"/>
+      <c r="D35" s="107" t="n"/>
+      <c r="E35" s="107" t="n"/>
+      <c r="F35" s="107" t="n"/>
+      <c r="G35" s="107" t="n"/>
+      <c r="H35" s="107" t="n"/>
+      <c r="I35" s="107" t="n"/>
+      <c r="J35" s="107" t="n"/>
+      <c r="K35" s="140" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="55" t="n"/>
@@ -4792,42 +4877,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
-      <c r="A1" s="91" t="n"/>
-      <c r="B1" s="92" t="n"/>
-      <c r="C1" s="93" t="inlineStr">
+      <c r="A1" s="93" t="n"/>
+      <c r="B1" s="94" t="n"/>
+      <c r="C1" s="95" t="inlineStr">
         <is>
           <t>Cadastros</t>
         </is>
       </c>
-      <c r="D1" s="94" t="n"/>
-      <c r="E1" s="94" t="n"/>
-      <c r="F1" s="94" t="n"/>
-      <c r="G1" s="92" t="n"/>
-      <c r="H1" s="95">
+      <c r="D1" s="96" t="n"/>
+      <c r="E1" s="96" t="n"/>
+      <c r="F1" s="96" t="n"/>
+      <c r="G1" s="94" t="n"/>
+      <c r="H1" s="97">
         <f>"Rev. "&amp;'Leia-me'!$D$15&amp;"   ·   "&amp;'Leia-me'!$D$16</f>
         <v/>
       </c>
-      <c r="I1" s="94" t="n"/>
-      <c r="J1" s="92" t="n"/>
+      <c r="I1" s="96" t="n"/>
+      <c r="J1" s="94" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="96" t="n"/>
-      <c r="B2" s="97" t="n"/>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="A2" s="98" t="n"/>
+      <c r="B2" s="99" t="n"/>
+      <c r="C2" s="100" t="inlineStr">
         <is>
           <t>Objetivo: Cadastre aqui os itens usados nas listas (▼) das outras abas.</t>
         </is>
       </c>
-      <c r="D2" s="99" t="n"/>
-      <c r="E2" s="99" t="n"/>
-      <c r="F2" s="99" t="n"/>
-      <c r="G2" s="97" t="n"/>
-      <c r="H2" s="98">
+      <c r="D2" s="101" t="n"/>
+      <c r="E2" s="101" t="n"/>
+      <c r="F2" s="101" t="n"/>
+      <c r="G2" s="99" t="n"/>
+      <c r="H2" s="100">
         <f>"Elaborado: "&amp;'Leia-me'!$D$13&amp;"   ·   Aprovado: "&amp;'Leia-me'!$D$14</f>
         <v/>
       </c>
-      <c r="I2" s="99" t="n"/>
-      <c r="J2" s="97" t="n"/>
+      <c r="I2" s="101" t="n"/>
+      <c r="J2" s="99" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="72" t="inlineStr">
@@ -4850,17 +4935,17 @@
           <t>Setor ▼</t>
         </is>
       </c>
-      <c r="F3" s="139" t="inlineStr">
+      <c r="F3" s="141" t="inlineStr">
         <is>
           <t>Responsável</t>
         </is>
       </c>
-      <c r="H3" s="139" t="inlineStr">
+      <c r="H3" s="141" t="inlineStr">
         <is>
           <t>Família de equipamento</t>
         </is>
       </c>
-      <c r="J3" s="139" t="inlineStr">
+      <c r="J3" s="141" t="inlineStr">
         <is>
           <t>Setor</t>
         </is>
@@ -4905,231 +4990,231 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="76" t="n"/>
-      <c r="B5" s="140" t="n"/>
-      <c r="C5" s="140" t="n"/>
-      <c r="D5" s="141" t="n"/>
+      <c r="B5" s="82" t="n"/>
+      <c r="C5" s="82" t="n"/>
+      <c r="D5" s="83" t="n"/>
       <c r="F5" s="142" t="n"/>
       <c r="H5" s="142" t="n"/>
       <c r="J5" s="142" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="76" t="n"/>
-      <c r="B6" s="140" t="n"/>
-      <c r="C6" s="140" t="n"/>
-      <c r="D6" s="141" t="n"/>
+      <c r="B6" s="82" t="n"/>
+      <c r="C6" s="82" t="n"/>
+      <c r="D6" s="83" t="n"/>
       <c r="F6" s="142" t="n"/>
       <c r="H6" s="142" t="n"/>
       <c r="J6" s="142" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="76" t="n"/>
-      <c r="B7" s="140" t="n"/>
-      <c r="C7" s="140" t="n"/>
-      <c r="D7" s="141" t="n"/>
+      <c r="B7" s="82" t="n"/>
+      <c r="C7" s="82" t="n"/>
+      <c r="D7" s="83" t="n"/>
       <c r="F7" s="142" t="n"/>
       <c r="H7" s="142" t="n"/>
       <c r="J7" s="142" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="76" t="n"/>
-      <c r="B8" s="140" t="n"/>
-      <c r="C8" s="140" t="n"/>
-      <c r="D8" s="141" t="n"/>
+      <c r="B8" s="82" t="n"/>
+      <c r="C8" s="82" t="n"/>
+      <c r="D8" s="83" t="n"/>
       <c r="F8" s="142" t="n"/>
       <c r="H8" s="142" t="n"/>
       <c r="J8" s="142" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="76" t="n"/>
-      <c r="B9" s="140" t="n"/>
-      <c r="C9" s="140" t="n"/>
-      <c r="D9" s="141" t="n"/>
+      <c r="B9" s="82" t="n"/>
+      <c r="C9" s="82" t="n"/>
+      <c r="D9" s="83" t="n"/>
       <c r="F9" s="142" t="n"/>
       <c r="H9" s="142" t="n"/>
       <c r="J9" s="142" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="76" t="n"/>
-      <c r="B10" s="140" t="n"/>
-      <c r="C10" s="140" t="n"/>
-      <c r="D10" s="141" t="n"/>
+      <c r="B10" s="82" t="n"/>
+      <c r="C10" s="82" t="n"/>
+      <c r="D10" s="83" t="n"/>
       <c r="F10" s="142" t="n"/>
       <c r="H10" s="142" t="n"/>
       <c r="J10" s="142" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="76" t="n"/>
-      <c r="B11" s="140" t="n"/>
-      <c r="C11" s="140" t="n"/>
-      <c r="D11" s="141" t="n"/>
+      <c r="B11" s="82" t="n"/>
+      <c r="C11" s="82" t="n"/>
+      <c r="D11" s="83" t="n"/>
       <c r="F11" s="142" t="n"/>
       <c r="H11" s="142" t="n"/>
       <c r="J11" s="142" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="76" t="n"/>
-      <c r="B12" s="140" t="n"/>
-      <c r="C12" s="140" t="n"/>
-      <c r="D12" s="141" t="n"/>
+      <c r="B12" s="82" t="n"/>
+      <c r="C12" s="82" t="n"/>
+      <c r="D12" s="83" t="n"/>
       <c r="F12" s="142" t="n"/>
       <c r="H12" s="142" t="n"/>
       <c r="J12" s="142" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="76" t="n"/>
-      <c r="B13" s="140" t="n"/>
-      <c r="C13" s="140" t="n"/>
-      <c r="D13" s="141" t="n"/>
+      <c r="B13" s="82" t="n"/>
+      <c r="C13" s="82" t="n"/>
+      <c r="D13" s="83" t="n"/>
       <c r="F13" s="142" t="n"/>
       <c r="H13" s="142" t="n"/>
       <c r="J13" s="142" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="76" t="n"/>
-      <c r="B14" s="140" t="n"/>
-      <c r="C14" s="140" t="n"/>
-      <c r="D14" s="141" t="n"/>
+      <c r="B14" s="82" t="n"/>
+      <c r="C14" s="82" t="n"/>
+      <c r="D14" s="83" t="n"/>
       <c r="F14" s="142" t="n"/>
       <c r="H14" s="142" t="n"/>
       <c r="J14" s="142" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="76" t="n"/>
-      <c r="B15" s="140" t="n"/>
-      <c r="C15" s="140" t="n"/>
-      <c r="D15" s="141" t="n"/>
+      <c r="B15" s="82" t="n"/>
+      <c r="C15" s="82" t="n"/>
+      <c r="D15" s="83" t="n"/>
       <c r="F15" s="142" t="n"/>
       <c r="H15" s="142" t="n"/>
       <c r="J15" s="142" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="76" t="n"/>
-      <c r="B16" s="140" t="n"/>
-      <c r="C16" s="140" t="n"/>
-      <c r="D16" s="141" t="n"/>
+      <c r="B16" s="82" t="n"/>
+      <c r="C16" s="82" t="n"/>
+      <c r="D16" s="83" t="n"/>
       <c r="F16" s="142" t="n"/>
       <c r="H16" s="142" t="n"/>
       <c r="J16" s="142" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="76" t="n"/>
-      <c r="B17" s="140" t="n"/>
-      <c r="C17" s="140" t="n"/>
-      <c r="D17" s="141" t="n"/>
+      <c r="B17" s="82" t="n"/>
+      <c r="C17" s="82" t="n"/>
+      <c r="D17" s="83" t="n"/>
       <c r="F17" s="142" t="n"/>
       <c r="H17" s="142" t="n"/>
       <c r="J17" s="142" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="76" t="n"/>
-      <c r="B18" s="140" t="n"/>
-      <c r="C18" s="140" t="n"/>
-      <c r="D18" s="141" t="n"/>
+      <c r="B18" s="82" t="n"/>
+      <c r="C18" s="82" t="n"/>
+      <c r="D18" s="83" t="n"/>
       <c r="F18" s="142" t="n"/>
       <c r="H18" s="142" t="n"/>
       <c r="J18" s="142" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="76" t="n"/>
-      <c r="B19" s="140" t="n"/>
-      <c r="C19" s="140" t="n"/>
-      <c r="D19" s="141" t="n"/>
+      <c r="B19" s="82" t="n"/>
+      <c r="C19" s="82" t="n"/>
+      <c r="D19" s="83" t="n"/>
       <c r="F19" s="142" t="n"/>
       <c r="H19" s="142" t="n"/>
       <c r="J19" s="142" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="76" t="n"/>
-      <c r="B20" s="140" t="n"/>
-      <c r="C20" s="140" t="n"/>
-      <c r="D20" s="141" t="n"/>
+      <c r="B20" s="82" t="n"/>
+      <c r="C20" s="82" t="n"/>
+      <c r="D20" s="83" t="n"/>
       <c r="F20" s="142" t="n"/>
       <c r="H20" s="142" t="n"/>
       <c r="J20" s="142" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="76" t="n"/>
-      <c r="B21" s="140" t="n"/>
-      <c r="C21" s="140" t="n"/>
-      <c r="D21" s="141" t="n"/>
+      <c r="B21" s="82" t="n"/>
+      <c r="C21" s="82" t="n"/>
+      <c r="D21" s="83" t="n"/>
       <c r="F21" s="142" t="n"/>
       <c r="H21" s="142" t="n"/>
       <c r="J21" s="142" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="76" t="n"/>
-      <c r="B22" s="140" t="n"/>
-      <c r="C22" s="140" t="n"/>
-      <c r="D22" s="141" t="n"/>
+      <c r="B22" s="82" t="n"/>
+      <c r="C22" s="82" t="n"/>
+      <c r="D22" s="83" t="n"/>
       <c r="F22" s="142" t="n"/>
       <c r="H22" s="142" t="n"/>
       <c r="J22" s="142" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="76" t="n"/>
-      <c r="B23" s="140" t="n"/>
-      <c r="C23" s="140" t="n"/>
-      <c r="D23" s="141" t="n"/>
+      <c r="B23" s="82" t="n"/>
+      <c r="C23" s="82" t="n"/>
+      <c r="D23" s="83" t="n"/>
       <c r="F23" s="142" t="n"/>
       <c r="H23" s="142" t="n"/>
       <c r="J23" s="142" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="76" t="n"/>
-      <c r="B24" s="140" t="n"/>
-      <c r="C24" s="140" t="n"/>
-      <c r="D24" s="141" t="n"/>
+      <c r="B24" s="82" t="n"/>
+      <c r="C24" s="82" t="n"/>
+      <c r="D24" s="83" t="n"/>
       <c r="F24" s="142" t="n"/>
       <c r="H24" s="142" t="n"/>
       <c r="J24" s="142" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="76" t="n"/>
-      <c r="B25" s="140" t="n"/>
-      <c r="C25" s="140" t="n"/>
-      <c r="D25" s="141" t="n"/>
+      <c r="B25" s="82" t="n"/>
+      <c r="C25" s="82" t="n"/>
+      <c r="D25" s="83" t="n"/>
       <c r="F25" s="142" t="n"/>
       <c r="H25" s="142" t="n"/>
       <c r="J25" s="142" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="76" t="n"/>
-      <c r="B26" s="140" t="n"/>
-      <c r="C26" s="140" t="n"/>
-      <c r="D26" s="141" t="n"/>
+      <c r="B26" s="82" t="n"/>
+      <c r="C26" s="82" t="n"/>
+      <c r="D26" s="83" t="n"/>
       <c r="F26" s="142" t="n"/>
       <c r="H26" s="142" t="n"/>
       <c r="J26" s="142" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="76" t="n"/>
-      <c r="B27" s="140" t="n"/>
-      <c r="C27" s="140" t="n"/>
-      <c r="D27" s="141" t="n"/>
+      <c r="B27" s="82" t="n"/>
+      <c r="C27" s="82" t="n"/>
+      <c r="D27" s="83" t="n"/>
       <c r="F27" s="142" t="n"/>
       <c r="H27" s="142" t="n"/>
       <c r="J27" s="142" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="76" t="n"/>
-      <c r="B28" s="140" t="n"/>
-      <c r="C28" s="140" t="n"/>
-      <c r="D28" s="141" t="n"/>
+      <c r="B28" s="82" t="n"/>
+      <c r="C28" s="82" t="n"/>
+      <c r="D28" s="83" t="n"/>
       <c r="F28" s="142" t="n"/>
       <c r="H28" s="142" t="n"/>
       <c r="J28" s="142" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="83" t="n"/>
-      <c r="B29" s="143" t="n"/>
-      <c r="C29" s="143" t="n"/>
-      <c r="D29" s="144" t="n"/>
-      <c r="F29" s="145" t="n"/>
-      <c r="H29" s="145" t="n"/>
-      <c r="J29" s="145" t="n"/>
+      <c r="A29" s="84" t="n"/>
+      <c r="B29" s="90" t="n"/>
+      <c r="C29" s="90" t="n"/>
+      <c r="D29" s="91" t="n"/>
+      <c r="F29" s="143" t="n"/>
+      <c r="H29" s="143" t="n"/>
+      <c r="J29" s="143" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="90" t="inlineStr">
+      <c r="A30" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -5192,32 +5277,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
-      <c r="A1" s="91" t="n"/>
-      <c r="B1" s="92" t="n"/>
+      <c r="A1" s="93" t="n"/>
+      <c r="B1" s="94" t="n"/>
       <c r="C1" s="40" t="inlineStr">
         <is>
           <t>Revisões</t>
         </is>
       </c>
-      <c r="D1" s="95">
+      <c r="D1" s="97">
         <f>"Rev. "&amp;'Leia-me'!$D$15&amp;"   ·   "&amp;'Leia-me'!$D$16</f>
         <v/>
       </c>
-      <c r="E1" s="92" t="n"/>
+      <c r="E1" s="94" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="96" t="n"/>
-      <c r="B2" s="97" t="n"/>
+      <c r="A2" s="98" t="n"/>
+      <c r="B2" s="99" t="n"/>
       <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Objetivo: Registre cada alteração do modelo; a última linha alimenta Rev. e data do cabeçalho.</t>
         </is>
       </c>
-      <c r="D2" s="98">
+      <c r="D2" s="100">
         <f>"Elaborado: "&amp;'Leia-me'!$D$13&amp;"   ·   Aprovado: "&amp;'Leia-me'!$D$14</f>
         <v/>
       </c>
-      <c r="E2" s="97" t="n"/>
+      <c r="E2" s="99" t="n"/>
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="72" t="inlineStr">
@@ -5274,12 +5359,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="146" t="inlineStr">
+      <c r="A5" s="144" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B5" s="147" t="n">
+      <c r="B5" s="145" t="n">
         <v>46325</v>
       </c>
       <c r="C5" s="80" t="inlineStr">
@@ -5287,179 +5372,179 @@
           <t>Emissão inicial</t>
         </is>
       </c>
-      <c r="D5" s="140" t="n"/>
-      <c r="E5" s="141" t="n"/>
+      <c r="D5" s="82" t="n"/>
+      <c r="E5" s="83" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="146" t="n"/>
-      <c r="B6" s="147" t="n"/>
+      <c r="A6" s="144" t="n"/>
+      <c r="B6" s="145" t="n"/>
       <c r="C6" s="80" t="n"/>
-      <c r="D6" s="140" t="n"/>
-      <c r="E6" s="141" t="n"/>
+      <c r="D6" s="82" t="n"/>
+      <c r="E6" s="83" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="146" t="n"/>
-      <c r="B7" s="147" t="n"/>
+      <c r="A7" s="144" t="n"/>
+      <c r="B7" s="145" t="n"/>
       <c r="C7" s="80" t="n"/>
-      <c r="D7" s="140" t="n"/>
-      <c r="E7" s="141" t="n"/>
+      <c r="D7" s="82" t="n"/>
+      <c r="E7" s="83" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="146" t="n"/>
-      <c r="B8" s="147" t="n"/>
+      <c r="A8" s="144" t="n"/>
+      <c r="B8" s="145" t="n"/>
       <c r="C8" s="80" t="n"/>
-      <c r="D8" s="140" t="n"/>
-      <c r="E8" s="141" t="n"/>
+      <c r="D8" s="82" t="n"/>
+      <c r="E8" s="83" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="146" t="n"/>
-      <c r="B9" s="147" t="n"/>
+      <c r="A9" s="144" t="n"/>
+      <c r="B9" s="145" t="n"/>
       <c r="C9" s="80" t="n"/>
-      <c r="D9" s="140" t="n"/>
-      <c r="E9" s="141" t="n"/>
+      <c r="D9" s="82" t="n"/>
+      <c r="E9" s="83" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="146" t="n"/>
-      <c r="B10" s="147" t="n"/>
+      <c r="A10" s="144" t="n"/>
+      <c r="B10" s="145" t="n"/>
       <c r="C10" s="80" t="n"/>
-      <c r="D10" s="140" t="n"/>
-      <c r="E10" s="141" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="83" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="146" t="n"/>
-      <c r="B11" s="147" t="n"/>
+      <c r="A11" s="144" t="n"/>
+      <c r="B11" s="145" t="n"/>
       <c r="C11" s="80" t="n"/>
-      <c r="D11" s="140" t="n"/>
-      <c r="E11" s="141" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="83" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="146" t="n"/>
-      <c r="B12" s="147" t="n"/>
+      <c r="A12" s="144" t="n"/>
+      <c r="B12" s="145" t="n"/>
       <c r="C12" s="80" t="n"/>
-      <c r="D12" s="140" t="n"/>
-      <c r="E12" s="141" t="n"/>
+      <c r="D12" s="82" t="n"/>
+      <c r="E12" s="83" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="146" t="n"/>
-      <c r="B13" s="147" t="n"/>
+      <c r="A13" s="144" t="n"/>
+      <c r="B13" s="145" t="n"/>
       <c r="C13" s="80" t="n"/>
-      <c r="D13" s="140" t="n"/>
-      <c r="E13" s="141" t="n"/>
+      <c r="D13" s="82" t="n"/>
+      <c r="E13" s="83" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="146" t="n"/>
-      <c r="B14" s="147" t="n"/>
+      <c r="A14" s="144" t="n"/>
+      <c r="B14" s="145" t="n"/>
       <c r="C14" s="80" t="n"/>
-      <c r="D14" s="140" t="n"/>
-      <c r="E14" s="141" t="n"/>
+      <c r="D14" s="82" t="n"/>
+      <c r="E14" s="83" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="146" t="n"/>
-      <c r="B15" s="147" t="n"/>
+      <c r="A15" s="144" t="n"/>
+      <c r="B15" s="145" t="n"/>
       <c r="C15" s="80" t="n"/>
-      <c r="D15" s="140" t="n"/>
-      <c r="E15" s="141" t="n"/>
+      <c r="D15" s="82" t="n"/>
+      <c r="E15" s="83" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="146" t="n"/>
-      <c r="B16" s="147" t="n"/>
+      <c r="A16" s="144" t="n"/>
+      <c r="B16" s="145" t="n"/>
       <c r="C16" s="80" t="n"/>
-      <c r="D16" s="140" t="n"/>
-      <c r="E16" s="141" t="n"/>
+      <c r="D16" s="82" t="n"/>
+      <c r="E16" s="83" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="146" t="n"/>
-      <c r="B17" s="147" t="n"/>
+      <c r="A17" s="144" t="n"/>
+      <c r="B17" s="145" t="n"/>
       <c r="C17" s="80" t="n"/>
-      <c r="D17" s="140" t="n"/>
-      <c r="E17" s="141" t="n"/>
+      <c r="D17" s="82" t="n"/>
+      <c r="E17" s="83" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="146" t="n"/>
-      <c r="B18" s="147" t="n"/>
+      <c r="A18" s="144" t="n"/>
+      <c r="B18" s="145" t="n"/>
       <c r="C18" s="80" t="n"/>
-      <c r="D18" s="140" t="n"/>
-      <c r="E18" s="141" t="n"/>
+      <c r="D18" s="82" t="n"/>
+      <c r="E18" s="83" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="146" t="n"/>
-      <c r="B19" s="147" t="n"/>
+      <c r="A19" s="144" t="n"/>
+      <c r="B19" s="145" t="n"/>
       <c r="C19" s="80" t="n"/>
-      <c r="D19" s="140" t="n"/>
-      <c r="E19" s="141" t="n"/>
+      <c r="D19" s="82" t="n"/>
+      <c r="E19" s="83" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="146" t="n"/>
-      <c r="B20" s="147" t="n"/>
+      <c r="A20" s="144" t="n"/>
+      <c r="B20" s="145" t="n"/>
       <c r="C20" s="80" t="n"/>
-      <c r="D20" s="140" t="n"/>
-      <c r="E20" s="141" t="n"/>
+      <c r="D20" s="82" t="n"/>
+      <c r="E20" s="83" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="146" t="n"/>
-      <c r="B21" s="147" t="n"/>
+      <c r="A21" s="144" t="n"/>
+      <c r="B21" s="145" t="n"/>
       <c r="C21" s="80" t="n"/>
-      <c r="D21" s="140" t="n"/>
-      <c r="E21" s="141" t="n"/>
+      <c r="D21" s="82" t="n"/>
+      <c r="E21" s="83" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="146" t="n"/>
-      <c r="B22" s="147" t="n"/>
+      <c r="A22" s="144" t="n"/>
+      <c r="B22" s="145" t="n"/>
       <c r="C22" s="80" t="n"/>
-      <c r="D22" s="140" t="n"/>
-      <c r="E22" s="141" t="n"/>
+      <c r="D22" s="82" t="n"/>
+      <c r="E22" s="83" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="146" t="n"/>
-      <c r="B23" s="147" t="n"/>
+      <c r="A23" s="144" t="n"/>
+      <c r="B23" s="145" t="n"/>
       <c r="C23" s="80" t="n"/>
-      <c r="D23" s="140" t="n"/>
-      <c r="E23" s="141" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="83" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="146" t="n"/>
-      <c r="B24" s="147" t="n"/>
+      <c r="A24" s="144" t="n"/>
+      <c r="B24" s="145" t="n"/>
       <c r="C24" s="80" t="n"/>
-      <c r="D24" s="140" t="n"/>
-      <c r="E24" s="141" t="n"/>
+      <c r="D24" s="82" t="n"/>
+      <c r="E24" s="83" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="146" t="n"/>
-      <c r="B25" s="147" t="n"/>
+      <c r="A25" s="144" t="n"/>
+      <c r="B25" s="145" t="n"/>
       <c r="C25" s="80" t="n"/>
-      <c r="D25" s="140" t="n"/>
-      <c r="E25" s="141" t="n"/>
+      <c r="D25" s="82" t="n"/>
+      <c r="E25" s="83" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="146" t="n"/>
-      <c r="B26" s="147" t="n"/>
+      <c r="A26" s="144" t="n"/>
+      <c r="B26" s="145" t="n"/>
       <c r="C26" s="80" t="n"/>
-      <c r="D26" s="140" t="n"/>
-      <c r="E26" s="141" t="n"/>
+      <c r="D26" s="82" t="n"/>
+      <c r="E26" s="83" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="146" t="n"/>
-      <c r="B27" s="147" t="n"/>
+      <c r="A27" s="144" t="n"/>
+      <c r="B27" s="145" t="n"/>
       <c r="C27" s="80" t="n"/>
-      <c r="D27" s="140" t="n"/>
-      <c r="E27" s="141" t="n"/>
+      <c r="D27" s="82" t="n"/>
+      <c r="E27" s="83" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="146" t="n"/>
-      <c r="B28" s="147" t="n"/>
+      <c r="A28" s="144" t="n"/>
+      <c r="B28" s="145" t="n"/>
       <c r="C28" s="80" t="n"/>
-      <c r="D28" s="140" t="n"/>
-      <c r="E28" s="141" t="n"/>
+      <c r="D28" s="82" t="n"/>
+      <c r="E28" s="83" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="148" t="n"/>
-      <c r="B29" s="149" t="n"/>
-      <c r="C29" s="87" t="n"/>
-      <c r="D29" s="143" t="n"/>
-      <c r="E29" s="144" t="n"/>
+      <c r="A29" s="146" t="n"/>
+      <c r="B29" s="147" t="n"/>
+      <c r="C29" s="88" t="n"/>
+      <c r="D29" s="90" t="n"/>
+      <c r="E29" s="91" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="90" t="inlineStr">
+      <c r="A30" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
